--- a/excel/metricas-diarias/02_Metricas_Diarias_Embudo_Webinar_Gratuito.xlsx
+++ b/excel/metricas-diarias/02_Metricas_Diarias_Embudo_Webinar_Gratuito.xlsx
@@ -1264,24 +1264,12 @@
       <c r="J6" s="13" t="n">
         <v>575</v>
       </c>
-      <c r="K6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="13" t="n">
-        <v>0</v>
-      </c>
+      <c r="K6" s="13" t="n"/>
+      <c r="L6" s="13" t="n"/>
+      <c r="M6" s="13" t="n"/>
+      <c r="N6" s="13" t="n"/>
+      <c r="O6" s="13" t="n"/>
+      <c r="P6" s="13" t="n"/>
       <c r="Q6" s="14">
         <f>IF(COUNT(C6:P6)=0,"",IFERROR(C6/D6*1000,0))</f>
         <v/>
@@ -1444,24 +1432,12 @@
       <c r="J7" s="13" t="n">
         <v>438</v>
       </c>
-      <c r="K7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="13" t="n">
-        <v>0</v>
-      </c>
+      <c r="K7" s="13" t="n"/>
+      <c r="L7" s="13" t="n"/>
+      <c r="M7" s="13" t="n"/>
+      <c r="N7" s="13" t="n"/>
+      <c r="O7" s="13" t="n"/>
+      <c r="P7" s="13" t="n"/>
       <c r="Q7" s="14">
         <f>IF(COUNT(C7:P7)=0,"",IFERROR(C7/D7*1000,0))</f>
         <v/>
@@ -1624,24 +1600,12 @@
       <c r="J8" s="13" t="n">
         <v>809</v>
       </c>
-      <c r="K8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="13" t="n">
-        <v>0</v>
-      </c>
+      <c r="K8" s="13" t="n"/>
+      <c r="L8" s="13" t="n"/>
+      <c r="M8" s="13" t="n"/>
+      <c r="N8" s="13" t="n"/>
+      <c r="O8" s="13" t="n"/>
+      <c r="P8" s="13" t="n"/>
       <c r="Q8" s="14">
         <f>IF(COUNT(C8:P8)=0,"",IFERROR(C8/D8*1000,0))</f>
         <v/>
@@ -1805,19 +1769,19 @@
         <v>393</v>
       </c>
       <c r="K9" s="13" t="n">
-        <v>545</v>
+        <v>888</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>734</v>
+        <v>1195</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="N9" s="13" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P9" s="13" t="n">
         <v>0</v>
@@ -1961,44 +1925,44 @@
         <v/>
       </c>
       <c r="C10" s="9" t="n">
-        <v>927</v>
+        <v>861</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>205154</v>
+        <v>185087</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>132314</v>
+        <v>123398</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>4513</v>
+        <v>4231</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>4220</v>
+        <v>3769</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>961</v>
+        <v>821</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>576</v>
+        <v>492</v>
       </c>
       <c r="J10" s="13" t="n">
-        <v>644</v>
+        <v>550</v>
       </c>
       <c r="K10" s="13" t="n"/>
       <c r="L10" s="13" t="n">
-        <v>960</v>
+        <v>1590</v>
       </c>
       <c r="M10" s="13" t="n">
-        <v>27</v>
+        <v>110</v>
       </c>
       <c r="N10" s="13" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="P10" s="13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q10" s="14">
         <f>IF(COUNT(C10:P10)=0,"",IFERROR(C10/D10*1000,0))</f>
@@ -2139,44 +2103,44 @@
         <v/>
       </c>
       <c r="C11" s="9" t="n">
-        <v>959</v>
+        <v>927</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>190525</v>
+        <v>196209</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>117428</v>
+        <v>136874</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>4401</v>
+        <v>4037</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>3785</v>
+        <v>3449</v>
       </c>
       <c r="H11" s="13" t="n">
-        <v>814</v>
+        <v>711</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>488</v>
+        <v>427</v>
       </c>
       <c r="J11" s="13" t="n">
-        <v>545</v>
+        <v>477</v>
       </c>
       <c r="K11" s="13" t="n"/>
       <c r="L11" s="13" t="n">
-        <v>383</v>
+        <v>619</v>
       </c>
       <c r="M11" s="13" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="N11" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="O11" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="O11" s="13" t="n">
+      <c r="P11" s="13" t="n">
         <v>1</v>
-      </c>
-      <c r="P11" s="13" t="n">
-        <v>0</v>
       </c>
       <c r="Q11" s="14">
         <f>IF(COUNT(C11:P11)=0,"",IFERROR(C11/D11*1000,0))</f>
@@ -2317,47 +2281,35 @@
         <v/>
       </c>
       <c r="C12" s="9" t="n">
-        <v>769</v>
+        <v>928</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>160541</v>
+        <v>212061</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>109648</v>
+        <v>127372</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>3826</v>
+        <v>5054</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>3349</v>
+        <v>4004</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>573</v>
-      </c>
-      <c r="K12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="13" t="n">
-        <v>0</v>
-      </c>
+        <v>574</v>
+      </c>
+      <c r="K12" s="13" t="n"/>
+      <c r="L12" s="13" t="n"/>
+      <c r="M12" s="13" t="n"/>
+      <c r="N12" s="13" t="n"/>
+      <c r="O12" s="13" t="n"/>
+      <c r="P12" s="13" t="n"/>
       <c r="Q12" s="14">
         <f>IF(COUNT(C12:P12)=0,"",IFERROR(C12/D12*1000,0))</f>
         <v/>
@@ -2497,47 +2449,35 @@
         <v/>
       </c>
       <c r="C13" s="9" t="n">
-        <v>754</v>
+        <v>851</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>180168</v>
+        <v>169528</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>109345</v>
+        <v>115871</v>
       </c>
       <c r="F13" s="13" t="n">
-        <v>3935</v>
+        <v>3347</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>3950</v>
+        <v>3106</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>886</v>
+        <v>762</v>
       </c>
       <c r="I13" s="13" t="n">
-        <v>532</v>
+        <v>457</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>594</v>
-      </c>
-      <c r="K13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="13" t="n">
-        <v>0</v>
-      </c>
+        <v>511</v>
+      </c>
+      <c r="K13" s="13" t="n"/>
+      <c r="L13" s="13" t="n"/>
+      <c r="M13" s="13" t="n"/>
+      <c r="N13" s="13" t="n"/>
+      <c r="O13" s="13" t="n"/>
+      <c r="P13" s="13" t="n"/>
       <c r="Q13" s="14">
         <f>IF(COUNT(C13:P13)=0,"",IFERROR(C13/D13*1000,0))</f>
         <v/>
@@ -2677,47 +2617,35 @@
         <v/>
       </c>
       <c r="C14" s="9" t="n">
-        <v>884</v>
+        <v>772</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>184058</v>
+        <v>178757</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>129882</v>
+        <v>107228</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>3648</v>
+        <v>4176</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>3151</v>
+        <v>3414</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>806</v>
+        <v>737</v>
       </c>
       <c r="I14" s="13" t="n">
-        <v>483</v>
+        <v>442</v>
       </c>
       <c r="J14" s="13" t="n">
-        <v>540</v>
-      </c>
-      <c r="K14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="13" t="n">
-        <v>0</v>
-      </c>
+        <v>494</v>
+      </c>
+      <c r="K14" s="13" t="n"/>
+      <c r="L14" s="13" t="n"/>
+      <c r="M14" s="13" t="n"/>
+      <c r="N14" s="13" t="n"/>
+      <c r="O14" s="13" t="n"/>
+      <c r="P14" s="13" t="n"/>
       <c r="Q14" s="14">
         <f>IF(COUNT(C14:P14)=0,"",IFERROR(C14/D14*1000,0))</f>
         <v/>
@@ -2857,47 +2785,35 @@
         <v/>
       </c>
       <c r="C15" s="9" t="n">
-        <v>778</v>
+        <v>766</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>184196</v>
+        <v>158995</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>135800</v>
+        <v>114884</v>
       </c>
       <c r="F15" s="13" t="n">
-        <v>3624</v>
+        <v>3548</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>3494</v>
+        <v>3153</v>
       </c>
       <c r="H15" s="13" t="n">
-        <v>742</v>
+        <v>671</v>
       </c>
       <c r="I15" s="13" t="n">
-        <v>445</v>
+        <v>403</v>
       </c>
       <c r="J15" s="13" t="n">
-        <v>497</v>
-      </c>
-      <c r="K15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="13" t="n">
-        <v>0</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="K15" s="13" t="n"/>
+      <c r="L15" s="13" t="n"/>
+      <c r="M15" s="13" t="n"/>
+      <c r="N15" s="13" t="n"/>
+      <c r="O15" s="13" t="n"/>
+      <c r="P15" s="13" t="n"/>
       <c r="Q15" s="14">
         <f>IF(COUNT(C15:P15)=0,"",IFERROR(C15/D15*1000,0))</f>
         <v/>
@@ -3037,43 +2953,43 @@
         <v/>
       </c>
       <c r="C16" s="9" t="n">
-        <v>846</v>
+        <v>781</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>203120</v>
+        <v>167790</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>128274</v>
+        <v>123199</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>4073</v>
+        <v>3621</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>3792</v>
+        <v>3034</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>792</v>
+        <v>659</v>
       </c>
       <c r="I16" s="13" t="n">
-        <v>475</v>
+        <v>396</v>
       </c>
       <c r="J16" s="13" t="n">
-        <v>531</v>
+        <v>442</v>
       </c>
       <c r="K16" s="13" t="n">
-        <v>530</v>
+        <v>997</v>
       </c>
       <c r="L16" s="13" t="n">
-        <v>741</v>
+        <v>1268</v>
       </c>
       <c r="M16" s="13" t="n">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="N16" s="13" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="O16" s="13" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P16" s="13" t="n">
         <v>0</v>
@@ -3217,44 +3133,44 @@
         <v/>
       </c>
       <c r="C17" s="9" t="n">
-        <v>810</v>
+        <v>936</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>161652</v>
+        <v>223557</v>
       </c>
       <c r="E17" s="13" t="n">
-        <v>100453</v>
+        <v>152918</v>
       </c>
       <c r="F17" s="13" t="n">
-        <v>3389</v>
+        <v>5337</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>3332</v>
+        <v>4966</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>713</v>
+        <v>1033</v>
       </c>
       <c r="I17" s="13" t="n">
-        <v>428</v>
+        <v>620</v>
       </c>
       <c r="J17" s="13" t="n">
-        <v>478</v>
+        <v>692</v>
       </c>
       <c r="K17" s="13" t="n"/>
       <c r="L17" s="13" t="n">
-        <v>933</v>
+        <v>1588</v>
       </c>
       <c r="M17" s="13" t="n">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="N17" s="13" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="O17" s="13" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P17" s="13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="14">
         <f>IF(COUNT(C17:P17)=0,"",IFERROR(C17/D17*1000,0))</f>
@@ -3395,44 +3311,44 @@
         <v/>
       </c>
       <c r="C18" s="9" t="n">
-        <v>930</v>
+        <v>807</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>199839</v>
+        <v>168377</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>147361</v>
+        <v>117056</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>4913</v>
+        <v>3523</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>4117</v>
+        <v>2846</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>892</v>
+        <v>590</v>
       </c>
       <c r="I18" s="13" t="n">
-        <v>535</v>
+        <v>354</v>
       </c>
       <c r="J18" s="13" t="n">
-        <v>598</v>
+        <v>395</v>
       </c>
       <c r="K18" s="13" t="n"/>
       <c r="L18" s="13" t="n">
-        <v>341</v>
+        <v>606</v>
       </c>
       <c r="M18" s="13" t="n">
+        <v>31</v>
+      </c>
+      <c r="N18" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="O18" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="N18" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="O18" s="13" t="n">
+      <c r="P18" s="13" t="n">
         <v>1</v>
-      </c>
-      <c r="P18" s="13" t="n">
-        <v>0</v>
       </c>
       <c r="Q18" s="14">
         <f>IF(COUNT(C18:P18)=0,"",IFERROR(C18/D18*1000,0))</f>
@@ -3573,47 +3489,35 @@
         <v/>
       </c>
       <c r="C19" s="9" t="n">
-        <v>822</v>
+        <v>878</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>192013</v>
+        <v>201271</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>142609</v>
+        <v>135705</v>
       </c>
       <c r="F19" s="13" t="n">
-        <v>3809</v>
+        <v>4916</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>3496</v>
+        <v>4407</v>
       </c>
       <c r="H19" s="13" t="n">
-        <v>754</v>
+        <v>1032</v>
       </c>
       <c r="I19" s="13" t="n">
-        <v>453</v>
+        <v>619</v>
       </c>
       <c r="J19" s="13" t="n">
-        <v>505</v>
-      </c>
-      <c r="K19" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="13" t="n">
-        <v>0</v>
-      </c>
+        <v>691</v>
+      </c>
+      <c r="K19" s="13" t="n"/>
+      <c r="L19" s="13" t="n"/>
+      <c r="M19" s="13" t="n"/>
+      <c r="N19" s="13" t="n"/>
+      <c r="O19" s="13" t="n"/>
+      <c r="P19" s="13" t="n"/>
       <c r="Q19" s="14">
         <f>IF(COUNT(C19:P19)=0,"",IFERROR(C19/D19*1000,0))</f>
         <v/>
@@ -3753,47 +3657,35 @@
         <v/>
       </c>
       <c r="C20" s="9" t="n">
-        <v>831</v>
+        <v>792</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>186677</v>
+        <v>191875</v>
       </c>
       <c r="E20" s="13" t="n">
-        <v>112099</v>
+        <v>116497</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>4091</v>
+        <v>4543</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>3748</v>
+        <v>3843</v>
       </c>
       <c r="H20" s="13" t="n">
-        <v>938</v>
+        <v>818</v>
       </c>
       <c r="I20" s="13" t="n">
-        <v>563</v>
+        <v>491</v>
       </c>
       <c r="J20" s="13" t="n">
-        <v>628</v>
-      </c>
-      <c r="K20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="13" t="n">
-        <v>0</v>
-      </c>
+        <v>548</v>
+      </c>
+      <c r="K20" s="13" t="n"/>
+      <c r="L20" s="13" t="n"/>
+      <c r="M20" s="13" t="n"/>
+      <c r="N20" s="13" t="n"/>
+      <c r="O20" s="13" t="n"/>
+      <c r="P20" s="13" t="n"/>
       <c r="Q20" s="14">
         <f>IF(COUNT(C20:P20)=0,"",IFERROR(C20/D20*1000,0))</f>
         <v/>
@@ -3933,47 +3825,35 @@
         <v/>
       </c>
       <c r="C21" s="9" t="n">
-        <v>786</v>
+        <v>948</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>159046</v>
+        <v>227112</v>
       </c>
       <c r="E21" s="13" t="n">
-        <v>98517</v>
+        <v>136646</v>
       </c>
       <c r="F21" s="13" t="n">
-        <v>3289</v>
+        <v>5455</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>2739</v>
+        <v>5031</v>
       </c>
       <c r="H21" s="13" t="n">
-        <v>666</v>
+        <v>1135</v>
       </c>
       <c r="I21" s="13" t="n">
-        <v>400</v>
+        <v>681</v>
       </c>
       <c r="J21" s="13" t="n">
-        <v>446</v>
-      </c>
-      <c r="K21" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="13" t="n">
-        <v>0</v>
-      </c>
+        <v>761</v>
+      </c>
+      <c r="K21" s="13" t="n"/>
+      <c r="L21" s="13" t="n"/>
+      <c r="M21" s="13" t="n"/>
+      <c r="N21" s="13" t="n"/>
+      <c r="O21" s="13" t="n"/>
+      <c r="P21" s="13" t="n"/>
       <c r="Q21" s="14">
         <f>IF(COUNT(C21:P21)=0,"",IFERROR(C21/D21*1000,0))</f>
         <v/>
@@ -4113,47 +3993,35 @@
         <v/>
       </c>
       <c r="C22" s="9" t="n">
-        <v>795</v>
+        <v>762</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>159360</v>
+        <v>152433</v>
       </c>
       <c r="E22" s="13" t="n">
-        <v>97314</v>
+        <v>108430</v>
       </c>
       <c r="F22" s="13" t="n">
-        <v>3593</v>
+        <v>3518</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>3173</v>
+        <v>2982</v>
       </c>
       <c r="H22" s="13" t="n">
-        <v>660</v>
+        <v>739</v>
       </c>
       <c r="I22" s="13" t="n">
-        <v>396</v>
+        <v>443</v>
       </c>
       <c r="J22" s="13" t="n">
-        <v>442</v>
-      </c>
-      <c r="K22" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="13" t="n">
-        <v>0</v>
-      </c>
+        <v>495</v>
+      </c>
+      <c r="K22" s="13" t="n"/>
+      <c r="L22" s="13" t="n"/>
+      <c r="M22" s="13" t="n"/>
+      <c r="N22" s="13" t="n"/>
+      <c r="O22" s="13" t="n"/>
+      <c r="P22" s="13" t="n"/>
       <c r="Q22" s="14">
         <f>IF(COUNT(C22:P22)=0,"",IFERROR(C22/D22*1000,0))</f>
         <v/>
@@ -4293,43 +4161,43 @@
         <v/>
       </c>
       <c r="C23" s="9" t="n">
-        <v>952</v>
+        <v>815</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>225766</v>
+        <v>196294</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>143467</v>
+        <v>124289</v>
       </c>
       <c r="F23" s="13" t="n">
-        <v>4677</v>
+        <v>3872</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>4536</v>
+        <v>3257</v>
       </c>
       <c r="H23" s="13" t="n">
-        <v>1068</v>
+        <v>760</v>
       </c>
       <c r="I23" s="13" t="n">
-        <v>641</v>
+        <v>456</v>
       </c>
       <c r="J23" s="13" t="n">
-        <v>715</v>
+        <v>509</v>
       </c>
       <c r="K23" s="13" t="n">
-        <v>544</v>
+        <v>955</v>
       </c>
       <c r="L23" s="13" t="n">
-        <v>765</v>
+        <v>1251</v>
       </c>
       <c r="M23" s="13" t="n">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="N23" s="13" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="O23" s="13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P23" s="13" t="n">
         <v>0</v>
@@ -4473,44 +4341,44 @@
         <v/>
       </c>
       <c r="C24" s="9" t="n">
-        <v>902</v>
+        <v>943</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>223664</v>
+        <v>225544</v>
       </c>
       <c r="E24" s="13" t="n">
-        <v>159507</v>
+        <v>170098</v>
       </c>
       <c r="F24" s="13" t="n">
-        <v>4991</v>
+        <v>4687</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>4872</v>
+        <v>4163</v>
       </c>
       <c r="H24" s="13" t="n">
-        <v>1151</v>
+        <v>857</v>
       </c>
       <c r="I24" s="13" t="n">
-        <v>691</v>
+        <v>514</v>
       </c>
       <c r="J24" s="13" t="n">
-        <v>771</v>
+        <v>574</v>
       </c>
       <c r="K24" s="13" t="n"/>
       <c r="L24" s="13" t="n">
-        <v>960</v>
+        <v>1442</v>
       </c>
       <c r="M24" s="13" t="n">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="N24" s="13" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="O24" s="13" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P24" s="13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q24" s="14">
         <f>IF(COUNT(C24:P24)=0,"",IFERROR(C24/D24*1000,0))</f>
@@ -4651,44 +4519,44 @@
         <v/>
       </c>
       <c r="C25" s="9" t="n">
-        <v>943</v>
+        <v>872</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>225544</v>
+        <v>212536</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>170098</v>
+        <v>146539</v>
       </c>
       <c r="F25" s="13" t="n">
-        <v>4687</v>
+        <v>5114</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>4163</v>
+        <v>5134</v>
       </c>
       <c r="H25" s="13" t="n">
-        <v>857</v>
+        <v>1225</v>
       </c>
       <c r="I25" s="13" t="n">
-        <v>514</v>
+        <v>735</v>
       </c>
       <c r="J25" s="13" t="n">
-        <v>574</v>
+        <v>821</v>
       </c>
       <c r="K25" s="13" t="n"/>
       <c r="L25" s="13" t="n">
-        <v>394</v>
+        <v>614</v>
       </c>
       <c r="M25" s="13" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="N25" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="O25" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="O25" s="13" t="n">
+      <c r="P25" s="13" t="n">
         <v>1</v>
-      </c>
-      <c r="P25" s="13" t="n">
-        <v>0</v>
       </c>
       <c r="Q25" s="14">
         <f>IF(COUNT(C25:P25)=0,"",IFERROR(C25/D25*1000,0))</f>
@@ -4829,47 +4697,35 @@
         <v/>
       </c>
       <c r="C26" s="9" t="n">
-        <v>830</v>
+        <v>783</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>181307</v>
+        <v>195860</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>132595</v>
+        <v>147658</v>
       </c>
       <c r="F26" s="13" t="n">
-        <v>3857</v>
+        <v>4733</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>3797</v>
+        <v>4465</v>
       </c>
       <c r="H26" s="13" t="n">
-        <v>974</v>
+        <v>1141</v>
       </c>
       <c r="I26" s="13" t="n">
-        <v>584</v>
+        <v>685</v>
       </c>
       <c r="J26" s="13" t="n">
-        <v>653</v>
-      </c>
-      <c r="K26" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="13" t="n">
-        <v>0</v>
-      </c>
+        <v>765</v>
+      </c>
+      <c r="K26" s="13" t="n"/>
+      <c r="L26" s="13" t="n"/>
+      <c r="M26" s="13" t="n"/>
+      <c r="N26" s="13" t="n"/>
+      <c r="O26" s="13" t="n"/>
+      <c r="P26" s="13" t="n"/>
       <c r="Q26" s="14">
         <f>IF(COUNT(C26:P26)=0,"",IFERROR(C26/D26*1000,0))</f>
         <v/>
@@ -5009,47 +4865,35 @@
         <v/>
       </c>
       <c r="C27" s="9" t="n">
-        <v>896</v>
+        <v>885</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>195228</v>
+        <v>197511</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>142448</v>
+        <v>124772</v>
       </c>
       <c r="F27" s="13" t="n">
-        <v>3816</v>
+        <v>4156</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>3037</v>
+        <v>4189</v>
       </c>
       <c r="H27" s="13" t="n">
-        <v>767</v>
+        <v>865</v>
       </c>
       <c r="I27" s="13" t="n">
-        <v>460</v>
+        <v>519</v>
       </c>
       <c r="J27" s="13" t="n">
-        <v>514</v>
-      </c>
-      <c r="K27" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" s="13" t="n">
-        <v>0</v>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="K27" s="13" t="n"/>
+      <c r="L27" s="13" t="n"/>
+      <c r="M27" s="13" t="n"/>
+      <c r="N27" s="13" t="n"/>
+      <c r="O27" s="13" t="n"/>
+      <c r="P27" s="13" t="n"/>
       <c r="Q27" s="14">
         <f>IF(COUNT(C27:P27)=0,"",IFERROR(C27/D27*1000,0))</f>
         <v/>
@@ -5189,47 +5033,35 @@
         <v/>
       </c>
       <c r="C28" s="9" t="n">
-        <v>952</v>
+        <v>906</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>239064</v>
+        <v>183639</v>
       </c>
       <c r="E28" s="13" t="n">
-        <v>154332</v>
+        <v>115835</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>5237</v>
+        <v>4238</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>4974</v>
+        <v>4082</v>
       </c>
       <c r="H28" s="13" t="n">
-        <v>1094</v>
+        <v>1032</v>
       </c>
       <c r="I28" s="13" t="n">
-        <v>657</v>
+        <v>619</v>
       </c>
       <c r="J28" s="13" t="n">
-        <v>733</v>
-      </c>
-      <c r="K28" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" s="13" t="n">
-        <v>0</v>
-      </c>
+        <v>692</v>
+      </c>
+      <c r="K28" s="13" t="n"/>
+      <c r="L28" s="13" t="n"/>
+      <c r="M28" s="13" t="n"/>
+      <c r="N28" s="13" t="n"/>
+      <c r="O28" s="13" t="n"/>
+      <c r="P28" s="13" t="n"/>
       <c r="Q28" s="14">
         <f>IF(COUNT(C28:P28)=0,"",IFERROR(C28/D28*1000,0))</f>
         <v/>
@@ -5369,47 +5201,35 @@
         <v/>
       </c>
       <c r="C29" s="9" t="n">
-        <v>770</v>
+        <v>895</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>169160</v>
+        <v>181451</v>
       </c>
       <c r="E29" s="13" t="n">
-        <v>106704</v>
+        <v>111075</v>
       </c>
       <c r="F29" s="13" t="n">
-        <v>4079</v>
+        <v>3913</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>3880</v>
+        <v>3767</v>
       </c>
       <c r="H29" s="13" t="n">
-        <v>936</v>
+        <v>942</v>
       </c>
       <c r="I29" s="13" t="n">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="J29" s="13" t="n">
-        <v>627</v>
-      </c>
-      <c r="K29" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" s="13" t="n">
-        <v>0</v>
-      </c>
+        <v>631</v>
+      </c>
+      <c r="K29" s="13" t="n"/>
+      <c r="L29" s="13" t="n"/>
+      <c r="M29" s="13" t="n"/>
+      <c r="N29" s="13" t="n"/>
+      <c r="O29" s="13" t="n"/>
+      <c r="P29" s="13" t="n"/>
       <c r="Q29" s="14">
         <f>IF(COUNT(C29:P29)=0,"",IFERROR(C29/D29*1000,0))</f>
         <v/>
@@ -5549,43 +5369,43 @@
         <v/>
       </c>
       <c r="C30" s="9" t="n">
-        <v>942</v>
+        <v>883</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>217134</v>
+        <v>201856</v>
       </c>
       <c r="E30" s="13" t="n">
-        <v>138597</v>
+        <v>131953</v>
       </c>
       <c r="F30" s="13" t="n">
-        <v>5236</v>
+        <v>4557</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>5133</v>
+        <v>3688</v>
       </c>
       <c r="H30" s="13" t="n">
-        <v>1157</v>
+        <v>877</v>
       </c>
       <c r="I30" s="13" t="n">
-        <v>694</v>
+        <v>526</v>
       </c>
       <c r="J30" s="13" t="n">
-        <v>775</v>
+        <v>587</v>
       </c>
       <c r="K30" s="13" t="n">
-        <v>539</v>
+        <v>1011</v>
       </c>
       <c r="L30" s="13" t="n">
-        <v>680</v>
+        <v>1271</v>
       </c>
       <c r="M30" s="13" t="n">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="N30" s="13" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="O30" s="13" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P30" s="13" t="n">
         <v>0</v>
@@ -5729,44 +5549,44 @@
         <v/>
       </c>
       <c r="C31" s="9" t="n">
-        <v>872</v>
+        <v>834</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>188130</v>
+        <v>175448</v>
       </c>
       <c r="E31" s="13" t="n">
-        <v>129065</v>
+        <v>114736</v>
       </c>
       <c r="F31" s="13" t="n">
-        <v>4221</v>
+        <v>3805</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>3898</v>
+        <v>3702</v>
       </c>
       <c r="H31" s="13" t="n">
-        <v>806</v>
+        <v>766</v>
       </c>
       <c r="I31" s="13" t="n">
-        <v>484</v>
+        <v>460</v>
       </c>
       <c r="J31" s="13" t="n">
-        <v>540</v>
+        <v>514</v>
       </c>
       <c r="K31" s="13" t="n"/>
       <c r="L31" s="13" t="n">
-        <v>880</v>
+        <v>1545</v>
       </c>
       <c r="M31" s="13" t="n">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="N31" s="13" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="O31" s="13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="P31" s="13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q31" s="14">
         <f>IF(COUNT(C31:P31)=0,"",IFERROR(C31/D31*1000,0))</f>
@@ -5907,44 +5727,44 @@
         <v/>
       </c>
       <c r="C32" s="9" t="n">
-        <v>958</v>
+        <v>878</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>195200</v>
+        <v>195970</v>
       </c>
       <c r="E32" s="13" t="n">
-        <v>123376</v>
+        <v>139691</v>
       </c>
       <c r="F32" s="13" t="n">
-        <v>4179</v>
+        <v>4517</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>3974</v>
+        <v>4062</v>
       </c>
       <c r="H32" s="13" t="n">
-        <v>932</v>
+        <v>960</v>
       </c>
       <c r="I32" s="13" t="n">
-        <v>559</v>
+        <v>576</v>
       </c>
       <c r="J32" s="13" t="n">
-        <v>624</v>
+        <v>643</v>
       </c>
       <c r="K32" s="13" t="n"/>
       <c r="L32" s="13" t="n">
-        <v>369</v>
+        <v>630</v>
       </c>
       <c r="M32" s="13" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="N32" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="O32" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="O32" s="13" t="n">
+      <c r="P32" s="13" t="n">
         <v>1</v>
-      </c>
-      <c r="P32" s="13" t="n">
-        <v>0</v>
       </c>
       <c r="Q32" s="14">
         <f>IF(COUNT(C32:P32)=0,"",IFERROR(C32/D32*1000,0))</f>
@@ -6085,47 +5905,35 @@
         <v/>
       </c>
       <c r="C33" s="9" t="n">
-        <v>927</v>
+        <v>756</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>228762</v>
+        <v>176538</v>
       </c>
       <c r="E33" s="13" t="n">
-        <v>143868</v>
+        <v>112867</v>
       </c>
       <c r="F33" s="13" t="n">
-        <v>4465</v>
+        <v>3607</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>4116</v>
+        <v>2989</v>
       </c>
       <c r="H33" s="13" t="n">
-        <v>942</v>
+        <v>754</v>
       </c>
       <c r="I33" s="13" t="n">
-        <v>565</v>
+        <v>453</v>
       </c>
       <c r="J33" s="13" t="n">
-        <v>631</v>
-      </c>
-      <c r="K33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" s="13" t="n">
-        <v>0</v>
-      </c>
+        <v>505</v>
+      </c>
+      <c r="K33" s="13" t="n"/>
+      <c r="L33" s="13" t="n"/>
+      <c r="M33" s="13" t="n"/>
+      <c r="N33" s="13" t="n"/>
+      <c r="O33" s="13" t="n"/>
+      <c r="P33" s="13" t="n"/>
       <c r="Q33" s="14">
         <f>IF(COUNT(C33:P33)=0,"",IFERROR(C33/D33*1000,0))</f>
         <v/>
